--- a/data/trans_orig/P36BPD10_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P36BPD10_2023-Estudios-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el número de raciones pescado o mariscos que consumen a la semana en 2023</t>
+          <t>Población según el número de raciones pescado o mariscos que consumen a la semana en 2023 (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>38696</t>
+          <t>39271</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>63862</t>
+          <t>64758</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>58542</t>
+          <t>57386</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>83065</t>
+          <t>83848</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,47 +780,47 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
+          <t>11,12%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>184</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>118986</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>102372</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>139613</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>9,39%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>8,08%</t>
+        </is>
+      </c>
+      <c r="W4" s="2" t="inlineStr">
+        <is>
           <t>11,02%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>184</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>118986</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>103025</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>137101</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>9,39%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>8,13%</t>
-        </is>
-      </c>
-      <c r="W4" s="2" t="inlineStr">
-        <is>
-          <t>10,82%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>245689</t>
+          <t>246965</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>287571</t>
+          <t>289890</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>47,84%</t>
+          <t>48,09%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>55,99%</t>
+          <t>56,44%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>375606</t>
+          <t>372356</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>416378</t>
+          <t>415902</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>49,83%</t>
+          <t>49,4%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>55,24%</t>
+          <t>55,17%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>630201</t>
+          <t>631000</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>689526</t>
+          <t>692014</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>49,72%</t>
+          <t>49,79%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>54,41%</t>
+          <t>54,6%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>178295</t>
+          <t>175289</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>218142</t>
+          <t>215226</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>34,72%</t>
+          <t>34,13%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>42,47%</t>
+          <t>41,91%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>269900</t>
+          <t>270096</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>310173</t>
+          <t>312898</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>35,81%</t>
+          <t>35,83%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>41,15%</t>
+          <t>41,51%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>458244</t>
+          <t>458169</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>515826</t>
+          <t>515022</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>36,16%</t>
+          <t>36,15%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>40,7%</t>
+          <t>40,64%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>153447</t>
+          <t>159034</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>264250</t>
+          <t>261880</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>118343</t>
+          <t>124254</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>198626</t>
+          <t>198965</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>308082</t>
+          <t>309588</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>439524</t>
+          <t>445865</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,86%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1049799</t>
+          <t>1049704</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1524863</t>
+          <t>1483730</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>66,7%</t>
+          <t>64,9%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>687790</t>
+          <t>699389</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1082092</t>
+          <t>1082878</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>30,73%</t>
+          <t>31,25%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>48,35%</t>
+          <t>48,39%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1881654</t>
+          <t>1883896</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2515605</t>
+          <t>2568139</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>41,59%</t>
+          <t>41,64%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>55,61%</t>
+          <t>56,77%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>610481</t>
+          <t>630414</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>988311</t>
+          <t>991905</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>26,7%</t>
+          <t>27,58%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>43,23%</t>
+          <t>43,39%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>975362</t>
+          <t>977943</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1418716</t>
+          <t>1410906</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>43,59%</t>
+          <t>43,7%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>63,4%</t>
+          <t>63,05%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1698009</t>
+          <t>1674351</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>2322950</t>
+          <t>2304069</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>37,53%</t>
+          <t>37,01%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>51,35%</t>
+          <t>50,93%</t>
         </is>
       </c>
     </row>
@@ -1642,12 +1642,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>38795</t>
+          <t>39407</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>85479</t>
+          <t>84554</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1657,12 +1657,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>13,08%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1677,12 +1677,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>44945</t>
+          <t>46267</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>72132</t>
+          <t>73132</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1692,12 +1692,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1712,12 +1712,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>96145</t>
+          <t>94672</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>147176</t>
+          <t>148820</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>11,39%</t>
         </is>
       </c>
     </row>
@@ -1755,12 +1755,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>239836</t>
+          <t>240261</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>295257</t>
+          <t>295332</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1770,12 +1770,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>37,09%</t>
+          <t>37,16%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>45,66%</t>
+          <t>45,67%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1790,12 +1790,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>213181</t>
+          <t>213719</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>256851</t>
+          <t>257831</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1805,12 +1805,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>32,28%</t>
+          <t>32,36%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>38,89%</t>
+          <t>39,04%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1825,12 +1825,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>466971</t>
+          <t>468624</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>535454</t>
+          <t>538300</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1840,12 +1840,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>35,73%</t>
+          <t>35,85%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>40,97%</t>
+          <t>41,18%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>292412</t>
+          <t>293141</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>348860</t>
+          <t>348872</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,7 +1883,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>45,22%</t>
+          <t>45,33%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>346197</t>
+          <t>344144</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>392238</t>
+          <t>388140</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>52,42%</t>
+          <t>52,11%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>59,39%</t>
+          <t>58,77%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>654663</t>
+          <t>653101</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>725137</t>
+          <t>725183</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,7 +1953,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>50,09%</t>
+          <t>49,97%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2098,12 +2098,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>257431</t>
+          <t>261834</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>376809</t>
+          <t>384435</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2113,12 +2113,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2133,12 +2133,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>236675</t>
+          <t>240963</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>332404</t>
+          <t>329115</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2148,12 +2148,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2168,12 +2168,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>542148</t>
+          <t>532033</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>686283</t>
+          <t>685686</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2183,12 +2183,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>9,66%</t>
         </is>
       </c>
     </row>
@@ -2211,12 +2211,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1580520</t>
+          <t>1574754</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2117805</t>
+          <t>2146996</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2226,12 +2226,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>45,86%</t>
+          <t>45,69%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>61,45%</t>
+          <t>62,3%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2246,12 +2246,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1261118</t>
+          <t>1324359</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1729660</t>
+          <t>1721973</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2261,12 +2261,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>34,53%</t>
+          <t>36,26%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>47,36%</t>
+          <t>47,15%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2281,12 +2281,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3015856</t>
+          <t>3054897</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>3714492</t>
+          <t>3702582</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2296,12 +2296,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>42,49%</t>
+          <t>43,04%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>52,33%</t>
+          <t>52,16%</t>
         </is>
       </c>
     </row>
@@ -2324,12 +2324,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1085528</t>
+          <t>1053283</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1517147</t>
+          <t>1512619</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>31,5%</t>
+          <t>30,56%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>44,02%</t>
+          <t>43,89%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2359,12 +2359,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1622992</t>
+          <t>1634893</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>2181304</t>
+          <t>2099201</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2374,12 +2374,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>44,44%</t>
+          <t>44,77%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>59,73%</t>
+          <t>57,48%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2394,12 +2394,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>2856995</t>
+          <t>2850479</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>3512996</t>
+          <t>3484227</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2409,12 +2409,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>40,25%</t>
+          <t>40,16%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>49,49%</t>
+          <t>49,08%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P36BPD10_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P36BPD10_2023-Estudios-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>49458</t>
+          <t>58028</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>39271</t>
+          <t>44967</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>64758</t>
+          <t>72427</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,27 +760,27 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>69527</t>
+          <t>75911</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>57386</t>
+          <t>63409</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>83848</t>
+          <t>91204</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>118986</t>
+          <t>133939</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>102372</t>
+          <t>115123</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>139613</t>
+          <t>155383</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>11,12%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>267322</t>
+          <t>300610</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>246965</t>
+          <t>278005</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>289890</t>
+          <t>323145</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>52,05%</t>
+          <t>52,1%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>48,09%</t>
+          <t>48,18%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>56,44%</t>
+          <t>56,0%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>395019</t>
+          <t>438424</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>372356</t>
+          <t>416545</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>415902</t>
+          <t>461464</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>52,4%</t>
+          <t>53,46%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>49,4%</t>
+          <t>50,79%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>55,17%</t>
+          <t>56,26%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>662342</t>
+          <t>739034</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>631000</t>
+          <t>706405</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>692014</t>
+          <t>771134</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>52,26%</t>
+          <t>52,89%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>49,79%</t>
+          <t>50,56%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>54,6%</t>
+          <t>55,19%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>196803</t>
+          <t>218394</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>175289</t>
+          <t>195664</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>215226</t>
+          <t>240256</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>38,32%</t>
+          <t>37,85%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>34,13%</t>
+          <t>33,91%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>41,91%</t>
+          <t>41,64%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>289243</t>
+          <t>305839</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>270096</t>
+          <t>285772</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>312898</t>
+          <t>328479</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>38,37%</t>
+          <t>37,29%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>35,83%</t>
+          <t>34,84%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>41,51%</t>
+          <t>40,05%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>486047</t>
+          <t>524232</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>458169</t>
+          <t>493151</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>515022</t>
+          <t>557546</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>38,35%</t>
+          <t>37,52%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>36,15%</t>
+          <t>35,3%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>40,64%</t>
+          <t>39,9%</t>
         </is>
       </c>
     </row>
@@ -1064,17 +1064,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>513584</t>
+          <t>577032</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>513584</t>
+          <t>577032</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>513584</t>
+          <t>577032</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1099,17 +1099,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>753790</t>
+          <t>820174</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>753790</t>
+          <t>820174</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>753790</t>
+          <t>820174</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1134,17 +1134,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>1267374</t>
+          <t>1397205</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1267374</t>
+          <t>1397205</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1267374</t>
+          <t>1397205</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>220183</t>
+          <t>238186</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>159034</t>
+          <t>205598</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>261880</t>
+          <t>277220</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>164722</t>
+          <t>196133</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>124254</t>
+          <t>171337</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>198965</t>
+          <t>222172</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>384905</t>
+          <t>434319</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>309588</t>
+          <t>392068</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>445865</t>
+          <t>475507</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>10,81%</t>
         </is>
       </c>
     </row>
@@ -1294,67 +1294,67 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1199404</t>
+          <t>1059624</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1049704</t>
+          <t>1008317</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1483730</t>
+          <t>1116466</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>52,47%</t>
+          <t>47,59%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
+          <t>45,29%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>50,15%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>1282</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>997017</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>953114</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>1040615</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
           <t>45,92%</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>64,9%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>1282</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>951502</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>699389</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>1082878</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>42,52%</t>
-        </is>
-      </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>31,25%</t>
+          <t>43,89%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>48,39%</t>
+          <t>47,92%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>2150906</t>
+          <t>2056641</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1883896</t>
+          <t>1987610</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2568139</t>
+          <t>2129403</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>47,55%</t>
+          <t>46,77%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>41,64%</t>
+          <t>45,2%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>56,77%</t>
+          <t>48,42%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>866484</t>
+          <t>928534</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>630414</t>
+          <t>873163</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>991905</t>
+          <t>979330</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>37,9%</t>
+          <t>41,71%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>27,58%</t>
+          <t>39,22%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>43,39%</t>
+          <t>43,99%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>1121599</t>
+          <t>978242</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>977943</t>
+          <t>936048</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1410906</t>
+          <t>1021663</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>50,12%</t>
+          <t>45,05%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>43,7%</t>
+          <t>43,11%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>63,05%</t>
+          <t>47,05%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>1988082</t>
+          <t>1906776</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1674351</t>
+          <t>1839745</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>2304069</t>
+          <t>1975674</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>43,95%</t>
+          <t>43,36%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>37,01%</t>
+          <t>41,83%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>50,93%</t>
+          <t>44,92%</t>
         </is>
       </c>
     </row>
@@ -1520,17 +1520,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2286070</t>
+          <t>2226344</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2286070</t>
+          <t>2226344</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2286070</t>
+          <t>2226344</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1555,17 +1555,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2237823</t>
+          <t>2171392</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2237823</t>
+          <t>2171392</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2237823</t>
+          <t>2171392</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1590,17 +1590,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>4523893</t>
+          <t>4397736</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>4523893</t>
+          <t>4397736</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>4523893</t>
+          <t>4397736</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1637,32 +1637,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>56794</t>
+          <t>55362</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>39407</t>
+          <t>41171</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>84554</t>
+          <t>76402</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1672,67 +1672,67 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>57947</t>
+          <t>66074</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>46267</t>
+          <t>53336</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>73132</t>
+          <t>82189</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
+          <t>7,26%</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>11,18%</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>121436</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>101468</t>
+        </is>
+      </c>
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>144711</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>8,4%</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
           <t>7,01%</t>
         </is>
       </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>11,07%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>128</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>114741</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>94672</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>148820</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>8,78%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>7,24%</t>
-        </is>
-      </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>10,0%</t>
         </is>
       </c>
     </row>
@@ -1750,102 +1750,102 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>267419</t>
+          <t>300773</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>240261</t>
+          <t>272729</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>295332</t>
+          <t>328488</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
+          <t>42,27%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>38,33%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>46,16%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>340</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>261320</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>238411</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>285765</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>35,56%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>32,44%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>38,89%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>617</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>562094</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>526085</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>598275</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>38,86%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>36,37%</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
           <t>41,36%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>37,16%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>45,67%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>340</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>235257</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>213719</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>257831</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>35,62%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>32,36%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>39,04%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>617</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>502676</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>468624</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>538300</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>38,46%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>35,85%</t>
-        </is>
-      </c>
-      <c r="W13" s="2" t="inlineStr">
-        <is>
-          <t>41,18%</t>
         </is>
       </c>
     </row>
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>322410</t>
+          <t>355452</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>293141</t>
+          <t>328616</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>348872</t>
+          <t>386081</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>49,86%</t>
+          <t>49,95%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>45,33%</t>
+          <t>46,18%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>53,95%</t>
+          <t>54,26%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>367259</t>
+          <t>407482</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>344144</t>
+          <t>382520</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>388140</t>
+          <t>434013</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>55,61%</t>
+          <t>55,45%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>52,11%</t>
+          <t>52,05%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>58,77%</t>
+          <t>59,06%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>689669</t>
+          <t>762934</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>653101</t>
+          <t>726593</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>725183</t>
+          <t>801379</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>52,76%</t>
+          <t>52,74%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>49,97%</t>
+          <t>50,23%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>55,48%</t>
+          <t>55,4%</t>
         </is>
       </c>
     </row>
@@ -1976,17 +1976,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2011,17 +2011,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2046,17 +2046,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2093,32 +2093,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>326435</t>
+          <t>351576</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>261834</t>
+          <t>310357</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>384435</t>
+          <t>393559</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2128,32 +2128,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>292197</t>
+          <t>338118</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>240963</t>
+          <t>306231</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>329115</t>
+          <t>369065</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2163,32 +2163,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>618631</t>
+          <t>689695</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>532033</t>
+          <t>638576</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>685686</t>
+          <t>745827</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>10,3%</t>
         </is>
       </c>
     </row>
@@ -2206,32 +2206,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1734145</t>
+          <t>1661007</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1574754</t>
+          <t>1594970</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2146996</t>
+          <t>1724378</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>50,32%</t>
+          <t>47,26%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>45,69%</t>
+          <t>45,38%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>62,3%</t>
+          <t>49,06%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2241,32 +2241,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1581779</t>
+          <t>1696762</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1324359</t>
+          <t>1637630</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1721973</t>
+          <t>1754123</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>43,31%</t>
+          <t>45,53%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>36,26%</t>
+          <t>43,95%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>47,15%</t>
+          <t>47,07%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2276,32 +2276,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>3315923</t>
+          <t>3357769</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3054897</t>
+          <t>3275427</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>3702582</t>
+          <t>3447074</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>46,71%</t>
+          <t>46,37%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>43,04%</t>
+          <t>45,23%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>52,16%</t>
+          <t>47,6%</t>
         </is>
       </c>
     </row>
@@ -2319,32 +2319,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1385698</t>
+          <t>1502380</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1053283</t>
+          <t>1439264</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1512619</t>
+          <t>1564135</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>40,21%</t>
+          <t>42,74%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>30,56%</t>
+          <t>40,95%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>43,89%</t>
+          <t>44,5%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2354,32 +2354,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1778101</t>
+          <t>1691563</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1634893</t>
+          <t>1633818</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>2099201</t>
+          <t>1745101</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>48,69%</t>
+          <t>45,39%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>44,77%</t>
+          <t>43,84%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>57,48%</t>
+          <t>46,83%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2389,32 +2389,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>3163798</t>
+          <t>3193942</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>2850479</t>
+          <t>3110212</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>3484227</t>
+          <t>3279400</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>44,57%</t>
+          <t>44,11%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>40,16%</t>
+          <t>42,95%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>49,08%</t>
+          <t>45,29%</t>
         </is>
       </c>
     </row>
@@ -2432,17 +2432,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>3446277</t>
+          <t>3514963</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3446277</t>
+          <t>3514963</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3446277</t>
+          <t>3514963</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2467,17 +2467,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>3652076</t>
+          <t>3726443</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3652076</t>
+          <t>3726443</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3652076</t>
+          <t>3726443</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2502,17 +2502,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>7098353</t>
+          <t>7241406</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>7098353</t>
+          <t>7241406</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>7098353</t>
+          <t>7241406</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
